--- a/outputs/monitor_xlsx/20260316.xlsx
+++ b/outputs/monitor_xlsx/20260316.xlsx
@@ -544,10 +544,6 @@
           <t>-1.52%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-0.69%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+0.28%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>+1.96%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>-13.53%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>-3.39%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -695,7 +671,6 @@
           <t>-438.25億</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>-321.75億</t>
@@ -733,7 +708,6 @@
           <t>3.25億</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>33.28億</t>
@@ -744,8 +718,6 @@
           <t>166.42億</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -763,15 +735,11 @@
           <t>140.17%</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>143.91%</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -789,11 +757,6 @@
           <t>-469.3億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -811,15 +774,11 @@
           <t>18796口</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>14320口</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,7 +796,6 @@
           <t>-72.63億</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>-46.42億</t>
@@ -942,10 +900,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1067,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1102,6 +1056,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2317,6 +2272,112 @@
       <c r="W21" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>6160</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="E22" t="n">
+        <v>441</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>98</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-266</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-53</v>
+      </c>
+      <c r="I22" t="n">
+        <v>166</v>
+      </c>
+      <c r="J22" t="n">
+        <v>12</v>
+      </c>
+      <c r="K22" t="n">
+        <v>259</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1269</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-8986</v>
+      </c>
+      <c r="N22" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>偏空</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>-5.23</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2102</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>-443</v>
+      </c>
+      <c r="G23" t="n">
+        <v>828</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-80</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-113</v>
+      </c>
+      <c r="J23" t="n">
+        <v>60</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3303</v>
+      </c>
+      <c r="L23" t="n">
+        <v>15724</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-106277</v>
+      </c>
+      <c r="N23" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260316.xlsx
+++ b/outputs/monitor_xlsx/20260316.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -526,220 +526,232 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>美債10年殖利率</t>
+          <t>加權指數 (TWII)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>33342.51</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-1.52%</t>
-        </is>
-      </c>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>黃金指數 (GC=F)</t>
+          <t>櫃買指數 (OTC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5017.4$</t>
+          <t>317.19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.69%</t>
-        </is>
-      </c>
+          <t>+1.37%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>貨幣</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>美元/台幣匯率</t>
+          <t>台指近月期貨</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.9</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+0.28%</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>現貨</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>費半指數 (SOX)</t>
+          <t>美債10年殖利率</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7796.24</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+1.96%</t>
-        </is>
-      </c>
+          <t>-1.52%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>情緒</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>恐慌指數 (VIX)</t>
+          <t>黃金指數 (GC=F)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>4994.0$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-13.53%</t>
-        </is>
-      </c>
+          <t>-1.16%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>原物料</t>
+          <t>貨幣</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WTI原油期貨</t>
+          <t>美元/台幣匯率</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>95.36$</t>
+          <t>32.16</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-3.39%</t>
-        </is>
-      </c>
+          <t>+0.83%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>現貨</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>外資現貨</t>
+          <t>費半指數 (SOX)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-438.25億</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-321.75億</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-1608.75億</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-222.04億</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-4440.74億</t>
-        </is>
-      </c>
+          <t>7796.24</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>+1.96%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>情緒</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>投信現貨</t>
+          <t>恐慌指數 (VIX)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.25億</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>33.28億</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>166.42億</t>
-        </is>
-      </c>
+          <t>23.51</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-13.53%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>原物料</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>選擇權 P/C Ratio</t>
+          <t>WTI原油期貨</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>140.17%</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>143.91%</t>
-        </is>
-      </c>
+          <t>93.5$</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-5.28%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -749,12 +761,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>三大法人合計</t>
+          <t>外資現貨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-469.3億</t>
+          <t>-438.25億</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-447.35億</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-2236.75億</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>None億</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -766,54 +799,137 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>外資期貨未平倉</t>
+          <t>投信現貨</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18796口</t>
-        </is>
-      </c>
+          <t>3.25億</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14320口</t>
-        </is>
-      </c>
+          <t>60.51億</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>302.57億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>選擇權 P/C Ratio</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>None%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>三大法人合計</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-469.3億</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>外資期貨未平倉</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>18796口</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>14320口</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>結算</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>融資融券變化</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>-72.63億</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>-46.42億</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>-232.1億</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-10.47億</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-209.34億</t>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>None億</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -860,7 +976,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-321.75億</t>
+          <t>-447.35億</t>
         </is>
       </c>
     </row>
@@ -872,7 +988,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1608.75億</t>
+          <t>-2236.75億</t>
         </is>
       </c>
     </row>
@@ -884,7 +1000,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-222.04億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -896,9 +1012,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-4440.74億</t>
-        </is>
-      </c>
+          <t>None億</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -908,7 +1028,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>33.28億</t>
+          <t>60.51億</t>
         </is>
       </c>
     </row>
@@ -920,7 +1040,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>166.42億</t>
+          <t>302.57億</t>
         </is>
       </c>
     </row>
@@ -963,7 +1083,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-10.47億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -975,7 +1095,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-209.34億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -994,7 +1114,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>143.91%</t>
+          <t>None%</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1039,14 +1159,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1056,7 +1175,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1135,40 +1253,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1203,13 +1316,13 @@
         <v>-51029</v>
       </c>
       <c r="H4" t="n">
-        <v>-390551</v>
+        <v>-190373</v>
       </c>
       <c r="I4" t="n">
         <v>2764</v>
       </c>
       <c r="J4" t="n">
-        <v>13180</v>
+        <v>8232</v>
       </c>
       <c r="K4" t="n">
         <v>16888</v>
@@ -1218,20 +1331,12 @@
         <v>14592</v>
       </c>
       <c r="M4" t="n">
-        <v>67619</v>
+        <v>39493</v>
       </c>
       <c r="N4" t="n">
         <v>-4460464</v>
       </c>
-      <c r="O4" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1266,13 +1371,13 @@
         <v>-508</v>
       </c>
       <c r="H5" t="n">
-        <v>-728</v>
+        <v>-726</v>
       </c>
       <c r="I5" t="n">
         <v>-92</v>
       </c>
       <c r="J5" t="n">
-        <v>-646</v>
+        <v>-292</v>
       </c>
       <c r="K5" t="n">
         <v>55</v>
@@ -1281,20 +1386,12 @@
         <v>2837</v>
       </c>
       <c r="M5" t="n">
-        <v>13870</v>
+        <v>8358</v>
       </c>
       <c r="N5" t="n">
         <v>-78821</v>
       </c>
-      <c r="O5" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1329,13 +1426,13 @@
         <v>-863</v>
       </c>
       <c r="H6" t="n">
-        <v>361</v>
+        <v>-293</v>
       </c>
       <c r="I6" t="n">
         <v>-500</v>
       </c>
       <c r="J6" t="n">
-        <v>1187</v>
+        <v>920</v>
       </c>
       <c r="K6" t="n">
         <v>177</v>
@@ -1344,20 +1441,12 @@
         <v>5857</v>
       </c>
       <c r="M6" t="n">
-        <v>29325</v>
+        <v>17763</v>
       </c>
       <c r="N6" t="n">
         <v>-649051</v>
       </c>
-      <c r="O6" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1392,13 +1481,13 @@
         <v>-16174</v>
       </c>
       <c r="H7" t="n">
-        <v>-65568</v>
+        <v>-27731</v>
       </c>
       <c r="I7" t="n">
         <v>-802</v>
       </c>
       <c r="J7" t="n">
-        <v>3297</v>
+        <v>636</v>
       </c>
       <c r="K7" t="n">
         <v>447</v>
@@ -1407,20 +1496,12 @@
         <v>26249</v>
       </c>
       <c r="M7" t="n">
-        <v>124645</v>
+        <v>74796</v>
       </c>
       <c r="N7" t="n">
         <v>-6483131</v>
       </c>
-      <c r="O7" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1429,12 +1510,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1443,47 +1524,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>117</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>7.34</v>
+        <v>1390</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-2.11</v>
       </c>
       <c r="F8" t="n">
-        <v>201277</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>43234</v>
+        <v>4426</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>-769</v>
       </c>
       <c r="H8" t="n">
-        <v>-19089</v>
+        <v>-2478</v>
       </c>
       <c r="I8" t="n">
-        <v>-1390</v>
+        <v>-253</v>
       </c>
       <c r="J8" t="n">
-        <v>-1341</v>
+        <v>98</v>
       </c>
       <c r="K8" t="n">
-        <v>953</v>
+        <v>97</v>
       </c>
       <c r="L8" t="n">
-        <v>132205</v>
+        <v>2193</v>
       </c>
       <c r="M8" t="n">
-        <v>628690</v>
+        <v>5773</v>
       </c>
       <c r="N8" t="n">
-        <v>-1115017</v>
-      </c>
-      <c r="O8" t="n">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140186</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1492,12 +1565,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1506,47 +1579,39 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2585</v>
+        <v>1450</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>-4.44</v>
+        <v>-5.23</v>
       </c>
       <c r="F9" t="n">
-        <v>4463</v>
+        <v>2102</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-825</v>
+        <v>-443</v>
       </c>
       <c r="H9" t="n">
-        <v>-1450</v>
+        <v>1271</v>
       </c>
       <c r="I9" t="n">
-        <v>-20</v>
+        <v>-80</v>
       </c>
       <c r="J9" t="n">
-        <v>1001</v>
+        <v>-33</v>
       </c>
       <c r="K9" t="n">
-        <v>322</v>
+        <v>60</v>
       </c>
       <c r="L9" t="n">
-        <v>2009</v>
+        <v>3303</v>
       </c>
       <c r="M9" t="n">
-        <v>9308</v>
+        <v>9245</v>
       </c>
       <c r="N9" t="n">
-        <v>-89505</v>
-      </c>
-      <c r="O9" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106277</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1555,12 +1620,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1569,47 +1634,39 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3125</v>
+        <v>2585</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>-2.04</v>
+        <v>-4.44</v>
       </c>
       <c r="F10" t="n">
-        <v>1229</v>
+        <v>4463</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>-200</v>
+        <v>-825</v>
       </c>
       <c r="H10" t="n">
-        <v>-195</v>
+        <v>-1124</v>
       </c>
       <c r="I10" t="n">
-        <v>-141</v>
+        <v>-20</v>
       </c>
       <c r="J10" t="n">
-        <v>-142</v>
+        <v>828</v>
       </c>
       <c r="K10" t="n">
-        <v>85</v>
+        <v>322</v>
       </c>
       <c r="L10" t="n">
-        <v>5848</v>
+        <v>2009</v>
       </c>
       <c r="M10" t="n">
-        <v>29556</v>
+        <v>5892</v>
       </c>
       <c r="N10" t="n">
-        <v>-19748</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-1.88</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+        <v>-89505</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1644,13 +1701,13 @@
         <v>-161</v>
       </c>
       <c r="H11" t="n">
-        <v>18</v>
+        <v>-11</v>
       </c>
       <c r="I11" t="n">
         <v>-8</v>
       </c>
       <c r="J11" t="n">
-        <v>-280</v>
+        <v>-279</v>
       </c>
       <c r="K11" t="n">
         <v>29</v>
@@ -1659,20 +1716,12 @@
         <v>4332</v>
       </c>
       <c r="M11" t="n">
-        <v>22428</v>
+        <v>13288</v>
       </c>
       <c r="N11" t="n">
         <v>-19373</v>
       </c>
-      <c r="O11" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1681,58 +1730,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>1.01</v>
+        <v>6160</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>-1.99</v>
       </c>
       <c r="F12" t="n">
-        <v>510</v>
+        <v>441</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>162</v>
+        <v>98</v>
       </c>
       <c r="H12" t="n">
-        <v>-1657</v>
+        <v>-364</v>
       </c>
       <c r="I12" t="n">
-        <v>-11</v>
+        <v>-53</v>
       </c>
       <c r="J12" t="n">
-        <v>1463</v>
+        <v>219</v>
       </c>
       <c r="K12" t="n">
-        <v>-32</v>
+        <v>12</v>
       </c>
       <c r="L12" t="n">
-        <v>-56</v>
+        <v>259</v>
       </c>
       <c r="M12" t="n">
-        <v>-128</v>
+        <v>756</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8986</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1741,12 +1785,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>台新科</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1755,41 +1799,39 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>134.5</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
+        <v>2315</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>810</v>
+        <v>2730</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>26</v>
+        <v>162</v>
       </c>
       <c r="H13" t="n">
-        <v>359</v>
+        <v>-980</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-11</v>
       </c>
       <c r="J13" t="n">
-        <v>-501</v>
+        <v>1207</v>
       </c>
       <c r="K13" t="n">
-        <v>-6</v>
+        <v>-32</v>
       </c>
       <c r="L13" t="n">
-        <v>12</v>
+        <v>-56</v>
       </c>
       <c r="M13" t="n">
-        <v>-121</v>
+        <v>-152</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1812,19 +1854,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>427</v>
+        <v>449.5</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>6.35</v>
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>4135</v>
+        <v>3871</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>-5</v>
       </c>
       <c r="H14" t="n">
-        <v>-8</v>
+        <v>-28</v>
       </c>
       <c r="I14" t="n">
         <v>-647</v>
@@ -1839,17 +1881,12 @@
         <v>157</v>
       </c>
       <c r="M14" t="n">
-        <v>-511</v>
+        <v>-274</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1858,12 +1895,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1872,44 +1909,36 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1355</v>
+        <v>974</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>3.44</v>
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>389</v>
+        <v>1350</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>43</v>
+        <v>379</v>
       </c>
       <c r="H15" t="n">
-        <v>-123</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-3</v>
+        <v>737</v>
       </c>
       <c r="J15" t="n">
-        <v>-67</v>
+        <v>144</v>
       </c>
       <c r="K15" t="n">
-        <v>-17</v>
+        <v>27</v>
       </c>
       <c r="L15" t="n">
-        <v>-31</v>
+        <v>-82</v>
       </c>
       <c r="M15" t="n">
-        <v>-178</v>
+        <v>-302</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1918,466 +1947,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>耀登</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>187</v>
+        <v>1600</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>1.63</v>
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>4707</v>
+        <v>904</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H16" t="n">
-        <v>-433</v>
+        <v>72</v>
       </c>
       <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>28</v>
+      </c>
+      <c r="L16" t="n">
+        <v>136</v>
+      </c>
+      <c r="M16" t="n">
+        <v>121</v>
+      </c>
+      <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="K16" t="n">
-        <v>43</v>
-      </c>
-      <c r="L16" t="n">
-        <v>4537</v>
-      </c>
-      <c r="M16" t="n">
-        <v>20934</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-11204</v>
-      </c>
-      <c r="O16" t="n">
-        <v>6.01</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1390</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>-2.11</v>
-      </c>
-      <c r="F17" t="n">
-        <v>4426</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>-769</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-3262</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-253</v>
-      </c>
-      <c r="J17" t="n">
-        <v>265</v>
-      </c>
-      <c r="K17" t="n">
-        <v>97</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2193</v>
-      </c>
-      <c r="M17" t="n">
-        <v>9414</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-140186</v>
-      </c>
-      <c r="O17" t="n">
-        <v>-3.81</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>3163</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>波若威</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>960</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="F18" t="n">
-        <v>7281</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>-20</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-216</v>
-      </c>
-      <c r="I18" t="n">
-        <v>829</v>
-      </c>
-      <c r="J18" t="n">
-        <v>90</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-55</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1105</v>
-      </c>
-      <c r="M18" t="n">
-        <v>-659</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>漢唐</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>964</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>-4.55</v>
-      </c>
-      <c r="F19" t="n">
-        <v>4927</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>-2008</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-2244</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-260</v>
-      </c>
-      <c r="J19" t="n">
-        <v>962</v>
-      </c>
-      <c r="K19" t="n">
-        <v>402</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2279</v>
-      </c>
-      <c r="M19" t="n">
-        <v>10036</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-47615</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-8.539999999999999</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>6640</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>均豪</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>1065</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>9.91</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1150</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>130</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-44</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K20" t="n">
-        <v>28</v>
-      </c>
-      <c r="L20" t="n">
-        <v>136</v>
-      </c>
-      <c r="M20" t="n">
-        <v>67</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>732</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1050</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>379</v>
-      </c>
-      <c r="H21" t="n">
-        <v>819</v>
-      </c>
-      <c r="J21" t="n">
-        <v>144</v>
-      </c>
-      <c r="K21" t="n">
-        <v>27</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-82</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-475</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>6160</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>-1.99</v>
-      </c>
-      <c r="E22" t="n">
-        <v>441</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>98</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-266</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-53</v>
-      </c>
-      <c r="I22" t="n">
-        <v>166</v>
-      </c>
-      <c r="J22" t="n">
-        <v>12</v>
-      </c>
-      <c r="K22" t="n">
-        <v>259</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1269</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-8986</v>
-      </c>
-      <c r="N22" t="n">
-        <v>20.41</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1450</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>-5.23</v>
-      </c>
-      <c r="E23" t="n">
-        <v>2102</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>-443</v>
-      </c>
-      <c r="G23" t="n">
-        <v>828</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-80</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-113</v>
-      </c>
-      <c r="J23" t="n">
-        <v>60</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3303</v>
-      </c>
-      <c r="L23" t="n">
-        <v>15724</v>
-      </c>
-      <c r="M23" t="n">
-        <v>-106277</v>
-      </c>
-      <c r="N23" t="n">
-        <v>12.95</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>中性</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260316.xlsx
+++ b/outputs/monitor_xlsx/20260316.xlsx
@@ -544,10 +544,6 @@
           <t>-0.17%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+1.37%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,11 +583,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,10 +605,6 @@
           <t>-1.52%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,10 +627,6 @@
           <t>-1.16%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,10 +649,6 @@
           <t>+0.83%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,10 +671,6 @@
           <t>+1.96%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,10 +693,6 @@
           <t>-13.53%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -748,10 +715,6 @@
           <t>-5.28%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,7 +732,6 @@
           <t>-438.25億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-447.35億</t>
@@ -807,7 +769,6 @@
           <t>3.25億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>60.51億</t>
@@ -818,8 +779,6 @@
           <t>302.57億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,15 +796,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>None%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +818,6 @@
           <t>-469.3億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -885,15 +835,11 @@
           <t>18796口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>14320口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +857,6 @@
           <t>-72.63億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-46.42億</t>
@@ -1016,10 +961,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1141,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1175,6 +1117,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1994,6 +1937,54 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>367</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>-6.02</v>
+      </c>
+      <c r="E17" t="n">
+        <v>15891</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>-1403</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-3341</v>
+      </c>
+      <c r="H17" t="n">
+        <v>605</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1147</v>
+      </c>
+      <c r="J17" t="n">
+        <v>129</v>
+      </c>
+      <c r="K17" t="n">
+        <v>9182</v>
+      </c>
+      <c r="L17" t="n">
+        <v>38082</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-21942</v>
+      </c>
+      <c r="N17" t="n">
+        <v>22.74</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260316.xlsx
+++ b/outputs/monitor_xlsx/20260316.xlsx
@@ -961,7 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1238,7 +1237,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1246,26 +1245,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>75.59999999999999</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>-0.46</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>105392</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>-51029</v>
       </c>
       <c r="H4" t="n">
-        <v>-190373</v>
+        <v>-241402</v>
       </c>
       <c r="I4" t="n">
         <v>2764</v>
       </c>
       <c r="J4" t="n">
-        <v>8232</v>
+        <v>10996</v>
       </c>
       <c r="K4" t="n">
         <v>16888</v>
@@ -1274,11 +1273,14 @@
         <v>14592</v>
       </c>
       <c r="M4" t="n">
-        <v>39493</v>
+        <v>67824</v>
       </c>
       <c r="N4" t="n">
         <v>-4460464</v>
       </c>
+      <c r="O4" t="n">
+        <v>-1.41</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1301,26 +1303,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>909</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>-1.3</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>2038</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>-508</v>
       </c>
       <c r="H5" t="n">
-        <v>-726</v>
+        <v>-1234</v>
       </c>
       <c r="I5" t="n">
         <v>-92</v>
       </c>
       <c r="J5" t="n">
-        <v>-292</v>
+        <v>-384</v>
       </c>
       <c r="K5" t="n">
         <v>55</v>
@@ -1329,11 +1331,14 @@
         <v>2837</v>
       </c>
       <c r="M5" t="n">
-        <v>8358</v>
+        <v>13939</v>
       </c>
       <c r="N5" t="n">
         <v>-78821</v>
       </c>
+      <c r="O5" t="n">
+        <v>-4.58</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1356,26 +1361,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1360</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>-1.81</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>6238</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>-863</v>
       </c>
       <c r="H6" t="n">
-        <v>-293</v>
+        <v>-1156</v>
       </c>
       <c r="I6" t="n">
         <v>-500</v>
       </c>
       <c r="J6" t="n">
-        <v>920</v>
+        <v>420</v>
       </c>
       <c r="K6" t="n">
         <v>177</v>
@@ -1384,11 +1389,14 @@
         <v>5857</v>
       </c>
       <c r="M6" t="n">
-        <v>17763</v>
+        <v>29405</v>
       </c>
       <c r="N6" t="n">
         <v>-649051</v>
       </c>
+      <c r="O6" t="n">
+        <v>3.86</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1411,26 +1419,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1845</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>-1.07</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>35401</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>-16174</v>
       </c>
       <c r="H7" t="n">
-        <v>-27731</v>
+        <v>-43905</v>
       </c>
       <c r="I7" t="n">
         <v>-802</v>
       </c>
       <c r="J7" t="n">
-        <v>636</v>
+        <v>-166</v>
       </c>
       <c r="K7" t="n">
         <v>447</v>
@@ -1439,11 +1447,14 @@
         <v>26249</v>
       </c>
       <c r="M7" t="n">
-        <v>74796</v>
+        <v>125615</v>
       </c>
       <c r="N7" t="n">
         <v>-6483131</v>
       </c>
+      <c r="O7" t="n">
+        <v>-2.36</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1466,26 +1477,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1390</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>-2.11</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>4426</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>-769</v>
       </c>
       <c r="H8" t="n">
-        <v>-2478</v>
+        <v>-3247</v>
       </c>
       <c r="I8" t="n">
         <v>-253</v>
       </c>
       <c r="J8" t="n">
-        <v>98</v>
+        <v>-155</v>
       </c>
       <c r="K8" t="n">
         <v>97</v>
@@ -1494,11 +1505,14 @@
         <v>2193</v>
       </c>
       <c r="M8" t="n">
-        <v>5773</v>
+        <v>9799</v>
       </c>
       <c r="N8" t="n">
         <v>-140186</v>
       </c>
+      <c r="O8" t="n">
+        <v>0.16</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1521,26 +1535,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>1450</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>-5.23</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>2102</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>-443</v>
       </c>
       <c r="H9" t="n">
-        <v>1271</v>
+        <v>828</v>
       </c>
       <c r="I9" t="n">
         <v>-80</v>
       </c>
       <c r="J9" t="n">
-        <v>-33</v>
+        <v>-113</v>
       </c>
       <c r="K9" t="n">
         <v>60</v>
@@ -1549,11 +1563,14 @@
         <v>3303</v>
       </c>
       <c r="M9" t="n">
-        <v>9245</v>
+        <v>15724</v>
       </c>
       <c r="N9" t="n">
         <v>-106277</v>
       </c>
+      <c r="O9" t="n">
+        <v>12.95</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1576,26 +1593,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>2585</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>-4.44</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>4463</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>-825</v>
       </c>
       <c r="H10" t="n">
-        <v>-1124</v>
+        <v>-1948</v>
       </c>
       <c r="I10" t="n">
         <v>-20</v>
       </c>
       <c r="J10" t="n">
-        <v>828</v>
+        <v>808</v>
       </c>
       <c r="K10" t="n">
         <v>322</v>
@@ -1604,11 +1621,14 @@
         <v>2009</v>
       </c>
       <c r="M10" t="n">
-        <v>5892</v>
+        <v>9563</v>
       </c>
       <c r="N10" t="n">
         <v>-89505</v>
       </c>
+      <c r="O10" t="n">
+        <v>12.14</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1631,26 +1651,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="7" t="n">
         <v>1735</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>2.66</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>696</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>-161</v>
       </c>
       <c r="H11" t="n">
-        <v>-11</v>
+        <v>-172</v>
       </c>
       <c r="I11" t="n">
         <v>-8</v>
       </c>
       <c r="J11" t="n">
-        <v>-279</v>
+        <v>-287</v>
       </c>
       <c r="K11" t="n">
         <v>29</v>
@@ -1659,11 +1679,14 @@
         <v>4332</v>
       </c>
       <c r="M11" t="n">
-        <v>13288</v>
+        <v>22119</v>
       </c>
       <c r="N11" t="n">
         <v>-19373</v>
       </c>
+      <c r="O11" t="n">
+        <v>-9.94</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1686,26 +1709,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>6160</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>-1.99</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="6" t="n">
         <v>441</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>98</v>
       </c>
       <c r="H12" t="n">
-        <v>-364</v>
+        <v>-266</v>
       </c>
       <c r="I12" t="n">
         <v>-53</v>
       </c>
       <c r="J12" t="n">
-        <v>219</v>
+        <v>166</v>
       </c>
       <c r="K12" t="n">
         <v>12</v>
@@ -1714,11 +1737,14 @@
         <v>259</v>
       </c>
       <c r="M12" t="n">
-        <v>756</v>
+        <v>1269</v>
       </c>
       <c r="N12" t="n">
         <v>-8986</v>
       </c>
+      <c r="O12" t="n">
+        <v>20.41</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1741,26 +1767,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="7" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>162</v>
       </c>
       <c r="H13" t="n">
-        <v>-980</v>
+        <v>-818</v>
       </c>
       <c r="I13" t="n">
         <v>-11</v>
       </c>
       <c r="J13" t="n">
-        <v>1207</v>
+        <v>1196</v>
       </c>
       <c r="K13" t="n">
         <v>-32</v>
@@ -1769,11 +1795,14 @@
         <v>-56</v>
       </c>
       <c r="M13" t="n">
-        <v>-152</v>
+        <v>-170</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1796,26 +1825,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="7" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>-5</v>
       </c>
       <c r="H14" t="n">
-        <v>-28</v>
+        <v>-33</v>
       </c>
       <c r="I14" t="n">
         <v>-647</v>
       </c>
       <c r="J14" t="n">
-        <v>-1644</v>
+        <v>-2291</v>
       </c>
       <c r="K14" t="n">
         <v>-15</v>
@@ -1824,11 +1853,14 @@
         <v>157</v>
       </c>
       <c r="M14" t="n">
-        <v>-274</v>
+        <v>-51</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1851,20 +1883,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="6" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>379</v>
       </c>
       <c r="H15" t="n">
-        <v>737</v>
+        <v>1115</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>144</v>
@@ -1876,11 +1911,14 @@
         <v>-82</v>
       </c>
       <c r="M15" t="n">
-        <v>-302</v>
+        <v>-366</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1903,20 +1941,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="6" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>130</v>
       </c>
       <c r="H16" t="n">
-        <v>72</v>
+        <v>202</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>2</v>
@@ -1928,11 +1969,14 @@
         <v>136</v>
       </c>
       <c r="M16" t="n">
-        <v>121</v>
+        <v>207</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1950,41 +1994,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>367</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>-6.02</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="7" t="n">
         <v>15891</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="G17" s="7" t="n">
         <v>-1403</v>
       </c>
-      <c r="G17" t="n">
-        <v>-3341</v>
-      </c>
       <c r="H17" t="n">
+        <v>-2689</v>
+      </c>
+      <c r="I17" t="n">
         <v>605</v>
       </c>
-      <c r="I17" t="n">
-        <v>1147</v>
-      </c>
       <c r="J17" t="n">
+        <v>1242</v>
+      </c>
+      <c r="K17" t="n">
         <v>129</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>9182</v>
       </c>
-      <c r="L17" t="n">
-        <v>38082</v>
-      </c>
       <c r="M17" t="n">
+        <v>40461</v>
+      </c>
+      <c r="N17" t="n">
         <v>-21942</v>
       </c>
-      <c r="N17" t="n">
-        <v>22.74</v>
+      <c r="O17" t="n">
+        <v>25.74</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260316.xlsx
+++ b/outputs/monitor_xlsx/20260316.xlsx
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2036,6 +2036,165 @@
         <v>25.74</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1710</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4716</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>-685</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-6435</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-262</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-945</v>
+      </c>
+      <c r="K18" t="n">
+        <v>123</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6017</v>
+      </c>
+      <c r="M18" t="n">
+        <v>29416</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400947</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-2.66</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>549</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="F19" t="n">
+        <v>17800</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>3227</v>
+      </c>
+      <c r="H19" t="n">
+        <v>16856</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-60</v>
+      </c>
+      <c r="J19" t="n">
+        <v>158</v>
+      </c>
+      <c r="K19" t="n">
+        <v>765</v>
+      </c>
+      <c r="L19" t="n">
+        <v>36501</v>
+      </c>
+      <c r="M19" t="n">
+        <v>182287</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-392466</v>
+      </c>
+      <c r="O19" t="n">
+        <v>19.37</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>566</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F20" t="n">
+        <v>30633</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>-5462</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-4862</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5020</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4763</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1838</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9997</v>
+      </c>
+      <c r="M20" t="n">
+        <v>45041</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-161306</v>
+      </c>
+      <c r="O20" t="n">
+        <v>17.64</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
